--- a/artfynd/Lill-Lögdåberget V artfynd.xlsx
+++ b/artfynd/Lill-Lögdåberget V artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>126860469</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson, Vilhelm Kroon, Cajsa Björkén</t>
+          <t>Cajsa Björkén, Carl Jansson, Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
